--- a/output/version3/test/10-5/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C2" t="n">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D2" t="n">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="E2" t="n">
-        <v>381</v>
+        <v>523</v>
       </c>
       <c r="F2" t="n">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G2" t="n">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="H2" t="n">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="I2" t="n">
-        <v>474</v>
+        <v>407</v>
       </c>
       <c r="J2" t="n">
-        <v>517</v>
+        <v>462</v>
       </c>
       <c r="K2" t="n">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="L2" t="n">
-        <v>451.2</v>
+        <v>452.1</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="C3" t="n">
-        <v>586</v>
+        <v>504</v>
       </c>
       <c r="D3" t="n">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="E3" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F3" t="n">
-        <v>546</v>
+        <v>516</v>
       </c>
       <c r="G3" t="n">
-        <v>464</v>
+        <v>577</v>
       </c>
       <c r="H3" t="n">
-        <v>477</v>
+        <v>512</v>
       </c>
       <c r="I3" t="n">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="J3" t="n">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="K3" t="n">
-        <v>571</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>517.3</v>
+        <v>515.6</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C4" t="n">
-        <v>458</v>
+        <v>598</v>
       </c>
       <c r="D4" t="n">
-        <v>541</v>
+        <v>464</v>
       </c>
       <c r="E4" t="n">
-        <v>553</v>
+        <v>475</v>
       </c>
       <c r="F4" t="n">
+        <v>511</v>
+      </c>
+      <c r="G4" t="n">
         <v>529</v>
       </c>
-      <c r="G4" t="n">
-        <v>538</v>
-      </c>
       <c r="H4" t="n">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="I4" t="n">
-        <v>533</v>
+        <v>461</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="K4" t="n">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L4" t="n">
-        <v>515.2</v>
+        <v>502.3</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C5" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D5" t="n">
-        <v>520</v>
+        <v>478</v>
       </c>
       <c r="E5" t="n">
-        <v>461</v>
+        <v>554</v>
       </c>
       <c r="F5" t="n">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="G5" t="n">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="H5" t="n">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="I5" t="n">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="J5" t="n">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="K5" t="n">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="L5" t="n">
-        <v>475.8</v>
+        <v>488.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>417</v>
       </c>
       <c r="C6" t="n">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="D6" t="n">
-        <v>379</v>
+        <v>533</v>
       </c>
       <c r="E6" t="n">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F6" t="n">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="G6" t="n">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="H6" t="n">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="I6" t="n">
-        <v>411</v>
+        <v>480</v>
       </c>
       <c r="J6" t="n">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="K6" t="n">
-        <v>444</v>
+        <v>484</v>
       </c>
       <c r="L6" t="n">
-        <v>437</v>
+        <v>459.8</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C7" t="n">
+        <v>459</v>
+      </c>
+      <c r="D7" t="n">
+        <v>436</v>
+      </c>
+      <c r="E7" t="n">
+        <v>425</v>
+      </c>
+      <c r="F7" t="n">
+        <v>473</v>
+      </c>
+      <c r="G7" t="n">
+        <v>466</v>
+      </c>
+      <c r="H7" t="n">
         <v>458</v>
       </c>
-      <c r="D7" t="n">
-        <v>438</v>
-      </c>
-      <c r="E7" t="n">
-        <v>418</v>
-      </c>
-      <c r="F7" t="n">
-        <v>494</v>
-      </c>
-      <c r="G7" t="n">
-        <v>433</v>
-      </c>
-      <c r="H7" t="n">
-        <v>481</v>
-      </c>
       <c r="I7" t="n">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="J7" t="n">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="K7" t="n">
-        <v>485</v>
+        <v>379</v>
       </c>
       <c r="L7" t="n">
-        <v>461</v>
+        <v>446.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>527</v>
+        <v>474</v>
       </c>
       <c r="C8" t="n">
-        <v>558</v>
+        <v>478</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>513</v>
       </c>
       <c r="E8" t="n">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="F8" t="n">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="G8" t="n">
-        <v>471</v>
+        <v>510</v>
       </c>
       <c r="H8" t="n">
         <v>493</v>
       </c>
       <c r="I8" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="J8" t="n">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="K8" t="n">
-        <v>530</v>
+        <v>456</v>
       </c>
       <c r="L8" t="n">
-        <v>506.2</v>
+        <v>489.8</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>486</v>
+        <v>411</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="D9" t="n">
-        <v>468</v>
+        <v>412</v>
       </c>
       <c r="E9" t="n">
-        <v>418</v>
+        <v>488</v>
       </c>
       <c r="F9" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G9" t="n">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="H9" t="n">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="I9" t="n">
-        <v>471</v>
+        <v>409</v>
       </c>
       <c r="J9" t="n">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="K9" t="n">
-        <v>409</v>
+        <v>451</v>
       </c>
       <c r="L9" t="n">
-        <v>448.8</v>
+        <v>441.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>542</v>
+        <v>510</v>
       </c>
       <c r="C10" t="n">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="D10" t="n">
-        <v>493</v>
+        <v>540</v>
       </c>
       <c r="E10" t="n">
-        <v>471</v>
+        <v>511</v>
       </c>
       <c r="F10" t="n">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="G10" t="n">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="H10" t="n">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="I10" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J10" t="n">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="K10" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="L10" t="n">
-        <v>484.2</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
+        <v>464</v>
+      </c>
+      <c r="C11" t="n">
+        <v>438</v>
+      </c>
+      <c r="D11" t="n">
+        <v>433</v>
+      </c>
+      <c r="E11" t="n">
+        <v>439</v>
+      </c>
+      <c r="F11" t="n">
+        <v>477</v>
+      </c>
+      <c r="G11" t="n">
+        <v>440</v>
+      </c>
+      <c r="H11" t="n">
+        <v>415</v>
+      </c>
+      <c r="I11" t="n">
         <v>461</v>
       </c>
-      <c r="C11" t="n">
-        <v>430</v>
-      </c>
-      <c r="D11" t="n">
-        <v>423</v>
-      </c>
-      <c r="E11" t="n">
-        <v>457</v>
-      </c>
-      <c r="F11" t="n">
-        <v>456</v>
-      </c>
-      <c r="G11" t="n">
-        <v>431</v>
-      </c>
-      <c r="H11" t="n">
-        <v>431</v>
-      </c>
-      <c r="I11" t="n">
-        <v>479</v>
-      </c>
       <c r="J11" t="n">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="K11" t="n">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="L11" t="n">
-        <v>446.1</v>
+        <v>447.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>487</v>
+        <v>542</v>
       </c>
       <c r="C12" t="n">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="D12" t="n">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="E12" t="n">
-        <v>475</v>
+        <v>517</v>
       </c>
       <c r="F12" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G12" t="n">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="H12" t="n">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="I12" t="n">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="J12" t="n">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="K12" t="n">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="L12" t="n">
-        <v>501.1</v>
+        <v>510.8</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="C13" t="n">
-        <v>448</v>
+        <v>533</v>
       </c>
       <c r="D13" t="n">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="E13" t="n">
-        <v>415</v>
+        <v>524</v>
       </c>
       <c r="F13" t="n">
-        <v>578</v>
+        <v>477</v>
       </c>
       <c r="G13" t="n">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="H13" t="n">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="I13" t="n">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="J13" t="n">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="K13" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="L13" t="n">
-        <v>475.8</v>
+        <v>491.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>585</v>
+        <v>515</v>
       </c>
       <c r="C14" t="n">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="D14" t="n">
-        <v>507</v>
+        <v>456</v>
       </c>
       <c r="E14" t="n">
-        <v>603</v>
+        <v>453</v>
       </c>
       <c r="F14" t="n">
+        <v>477</v>
+      </c>
+      <c r="G14" t="n">
         <v>533</v>
       </c>
-      <c r="G14" t="n">
-        <v>509</v>
-      </c>
       <c r="H14" t="n">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="I14" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="J14" t="n">
-        <v>574</v>
+        <v>503</v>
       </c>
       <c r="K14" t="n">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="L14" t="n">
-        <v>534.1</v>
+        <v>497.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="C15" t="n">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="D15" t="n">
-        <v>442</v>
+        <v>487</v>
       </c>
       <c r="E15" t="n">
-        <v>425</v>
+        <v>491</v>
       </c>
       <c r="F15" t="n">
+        <v>459</v>
+      </c>
+      <c r="G15" t="n">
+        <v>440</v>
+      </c>
+      <c r="H15" t="n">
+        <v>416</v>
+      </c>
+      <c r="I15" t="n">
+        <v>446</v>
+      </c>
+      <c r="J15" t="n">
         <v>434</v>
       </c>
-      <c r="G15" t="n">
-        <v>446</v>
-      </c>
-      <c r="H15" t="n">
-        <v>455</v>
-      </c>
-      <c r="I15" t="n">
-        <v>487</v>
-      </c>
-      <c r="J15" t="n">
-        <v>452</v>
-      </c>
       <c r="K15" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="L15" t="n">
-        <v>446.6</v>
+        <v>446.4</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>523</v>
+        <v>449</v>
       </c>
       <c r="C16" t="n">
+        <v>509</v>
+      </c>
+      <c r="D16" t="n">
+        <v>428</v>
+      </c>
+      <c r="E16" t="n">
+        <v>441</v>
+      </c>
+      <c r="F16" t="n">
         <v>463</v>
       </c>
-      <c r="D16" t="n">
-        <v>449</v>
-      </c>
-      <c r="E16" t="n">
-        <v>477</v>
-      </c>
-      <c r="F16" t="n">
-        <v>454</v>
-      </c>
       <c r="G16" t="n">
-        <v>509</v>
+        <v>461</v>
       </c>
       <c r="H16" t="n">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="I16" t="n">
-        <v>508</v>
+        <v>451</v>
       </c>
       <c r="J16" t="n">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="K16" t="n">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="L16" t="n">
-        <v>482.3</v>
+        <v>464.1</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="C17" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D17" t="n">
+        <v>378</v>
+      </c>
+      <c r="E17" t="n">
+        <v>422</v>
+      </c>
+      <c r="F17" t="n">
         <v>466</v>
       </c>
-      <c r="E17" t="n">
-        <v>435</v>
-      </c>
-      <c r="F17" t="n">
-        <v>407</v>
-      </c>
       <c r="G17" t="n">
-        <v>508</v>
+        <v>400</v>
       </c>
       <c r="H17" t="n">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="I17" t="n">
-        <v>486</v>
+        <v>431</v>
       </c>
       <c r="J17" t="n">
-        <v>427</v>
+        <v>392</v>
       </c>
       <c r="K17" t="n">
-        <v>523</v>
+        <v>430</v>
       </c>
       <c r="L17" t="n">
-        <v>469.8</v>
+        <v>438.8</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
+        <v>498</v>
+      </c>
+      <c r="C18" t="n">
+        <v>474</v>
+      </c>
+      <c r="D18" t="n">
+        <v>493</v>
+      </c>
+      <c r="E18" t="n">
+        <v>468</v>
+      </c>
+      <c r="F18" t="n">
+        <v>475</v>
+      </c>
+      <c r="G18" t="n">
+        <v>421</v>
+      </c>
+      <c r="H18" t="n">
+        <v>458</v>
+      </c>
+      <c r="I18" t="n">
         <v>485</v>
       </c>
-      <c r="C18" t="n">
-        <v>426</v>
-      </c>
-      <c r="D18" t="n">
-        <v>448</v>
-      </c>
-      <c r="E18" t="n">
-        <v>497</v>
-      </c>
-      <c r="F18" t="n">
-        <v>449</v>
-      </c>
-      <c r="G18" t="n">
-        <v>462</v>
-      </c>
-      <c r="H18" t="n">
-        <v>451</v>
-      </c>
-      <c r="I18" t="n">
-        <v>461</v>
-      </c>
       <c r="J18" t="n">
-        <v>489</v>
+        <v>430</v>
       </c>
       <c r="K18" t="n">
         <v>548</v>
       </c>
       <c r="L18" t="n">
-        <v>471.6</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C19" t="n">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D19" t="n">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="E19" t="n">
-        <v>519</v>
+        <v>433</v>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>496</v>
       </c>
       <c r="G19" t="n">
-        <v>519</v>
+        <v>475</v>
       </c>
       <c r="H19" t="n">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="I19" t="n">
-        <v>454</v>
+        <v>520</v>
       </c>
       <c r="J19" t="n">
-        <v>542</v>
+        <v>575</v>
       </c>
       <c r="K19" t="n">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="L19" t="n">
-        <v>510.7</v>
+        <v>489.9</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>427</v>
+        <v>531</v>
       </c>
       <c r="C20" t="n">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="D20" t="n">
-        <v>494</v>
+        <v>550</v>
       </c>
       <c r="E20" t="n">
-        <v>520</v>
+        <v>464</v>
       </c>
       <c r="F20" t="n">
-        <v>555</v>
+        <v>428</v>
       </c>
       <c r="G20" t="n">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="H20" t="n">
+        <v>439</v>
+      </c>
+      <c r="I20" t="n">
+        <v>487</v>
+      </c>
+      <c r="J20" t="n">
+        <v>428</v>
+      </c>
+      <c r="K20" t="n">
+        <v>455</v>
+      </c>
+      <c r="L20" t="n">
         <v>469</v>
-      </c>
-      <c r="I20" t="n">
-        <v>514</v>
-      </c>
-      <c r="J20" t="n">
-        <v>541</v>
-      </c>
-      <c r="K20" t="n">
-        <v>463</v>
-      </c>
-      <c r="L20" t="n">
-        <v>496.8</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C21" t="n">
-        <v>415</v>
+        <v>478</v>
       </c>
       <c r="D21" t="n">
-        <v>480</v>
+        <v>426</v>
       </c>
       <c r="E21" t="n">
-        <v>384</v>
+        <v>464</v>
       </c>
       <c r="F21" t="n">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="G21" t="n">
-        <v>417</v>
+        <v>464</v>
       </c>
       <c r="H21" t="n">
         <v>432</v>
       </c>
       <c r="I21" t="n">
-        <v>464</v>
+        <v>429</v>
       </c>
       <c r="J21" t="n">
-        <v>400</v>
+        <v>469</v>
       </c>
       <c r="K21" t="n">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="L21" t="n">
-        <v>439.2</v>
+        <v>452.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>440</v>
+        <v>524</v>
       </c>
       <c r="C22" t="n">
-        <v>495</v>
+        <v>422</v>
       </c>
       <c r="D22" t="n">
-        <v>430</v>
+        <v>515</v>
       </c>
       <c r="E22" t="n">
-        <v>482</v>
+        <v>557</v>
       </c>
       <c r="F22" t="n">
-        <v>513</v>
+        <v>452</v>
       </c>
       <c r="G22" t="n">
-        <v>482</v>
+        <v>424</v>
       </c>
       <c r="H22" t="n">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I22" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="J22" t="n">
-        <v>488</v>
+        <v>536</v>
       </c>
       <c r="K22" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L22" t="n">
-        <v>470.2</v>
+        <v>480.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C23" t="n">
         <v>452</v>
       </c>
       <c r="D23" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="E23" t="n">
+        <v>436</v>
+      </c>
+      <c r="F23" t="n">
+        <v>441</v>
+      </c>
+      <c r="G23" t="n">
+        <v>362</v>
+      </c>
+      <c r="H23" t="n">
+        <v>435</v>
+      </c>
+      <c r="I23" t="n">
+        <v>460</v>
+      </c>
+      <c r="J23" t="n">
         <v>452</v>
       </c>
-      <c r="F23" t="n">
-        <v>448</v>
-      </c>
-      <c r="G23" t="n">
-        <v>407</v>
-      </c>
-      <c r="H23" t="n">
-        <v>432</v>
-      </c>
-      <c r="I23" t="n">
-        <v>448</v>
-      </c>
-      <c r="J23" t="n">
-        <v>374</v>
-      </c>
       <c r="K23" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L23" t="n">
-        <v>434.6</v>
+        <v>436.8</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="C24" t="n">
-        <v>460</v>
+        <v>382</v>
       </c>
       <c r="D24" t="n">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="E24" t="n">
-        <v>526</v>
+        <v>462</v>
       </c>
       <c r="F24" t="n">
+        <v>458</v>
+      </c>
+      <c r="G24" t="n">
+        <v>448</v>
+      </c>
+      <c r="H24" t="n">
         <v>438</v>
       </c>
-      <c r="G24" t="n">
-        <v>417</v>
-      </c>
-      <c r="H24" t="n">
-        <v>460</v>
-      </c>
       <c r="I24" t="n">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="J24" t="n">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="K24" t="n">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="L24" t="n">
-        <v>454.7</v>
+        <v>439.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
+        <v>369</v>
+      </c>
+      <c r="C25" t="n">
+        <v>402</v>
+      </c>
+      <c r="D25" t="n">
+        <v>382</v>
+      </c>
+      <c r="E25" t="n">
         <v>372</v>
       </c>
-      <c r="C25" t="n">
-        <v>393</v>
-      </c>
-      <c r="D25" t="n">
-        <v>408</v>
-      </c>
-      <c r="E25" t="n">
-        <v>395</v>
-      </c>
       <c r="F25" t="n">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="G25" t="n">
-        <v>463</v>
+        <v>392</v>
       </c>
       <c r="H25" t="n">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="I25" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="J25" t="n">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="K25" t="n">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="L25" t="n">
-        <v>398.3</v>
+        <v>395.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>492</v>
+        <v>560</v>
       </c>
       <c r="C26" t="n">
-        <v>553</v>
+        <v>755</v>
       </c>
       <c r="D26" t="n">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="E26" t="n">
-        <v>588</v>
+        <v>525</v>
       </c>
       <c r="F26" t="n">
-        <v>471</v>
+        <v>561</v>
       </c>
       <c r="G26" t="n">
-        <v>531</v>
+        <v>596</v>
       </c>
       <c r="H26" t="n">
-        <v>486</v>
+        <v>587</v>
       </c>
       <c r="I26" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J26" t="n">
-        <v>489</v>
+        <v>607</v>
       </c>
       <c r="K26" t="n">
-        <v>566</v>
+        <v>606</v>
       </c>
       <c r="L26" t="n">
-        <v>519.8</v>
+        <v>586</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C27" t="n">
+        <v>445</v>
+      </c>
+      <c r="D27" t="n">
+        <v>433</v>
+      </c>
+      <c r="E27" t="n">
+        <v>448</v>
+      </c>
+      <c r="F27" t="n">
+        <v>428</v>
+      </c>
+      <c r="G27" t="n">
+        <v>413</v>
+      </c>
+      <c r="H27" t="n">
+        <v>428</v>
+      </c>
+      <c r="I27" t="n">
+        <v>406</v>
+      </c>
+      <c r="J27" t="n">
+        <v>455</v>
+      </c>
+      <c r="K27" t="n">
         <v>408</v>
       </c>
-      <c r="D27" t="n">
-        <v>432</v>
-      </c>
-      <c r="E27" t="n">
-        <v>421</v>
-      </c>
-      <c r="F27" t="n">
-        <v>418</v>
-      </c>
-      <c r="G27" t="n">
-        <v>423</v>
-      </c>
-      <c r="H27" t="n">
-        <v>406</v>
-      </c>
-      <c r="I27" t="n">
-        <v>419</v>
-      </c>
-      <c r="J27" t="n">
-        <v>409</v>
-      </c>
-      <c r="K27" t="n">
-        <v>409</v>
-      </c>
       <c r="L27" t="n">
-        <v>418.6</v>
+        <v>430.2</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="C28" t="n">
-        <v>406</v>
+        <v>482</v>
       </c>
       <c r="D28" t="n">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E28" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F28" t="n">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="G28" t="n">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="H28" t="n">
         <v>468</v>
       </c>
       <c r="I28" t="n">
-        <v>444</v>
+        <v>483</v>
       </c>
       <c r="J28" t="n">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="K28" t="n">
-        <v>411</v>
+        <v>457</v>
       </c>
       <c r="L28" t="n">
-        <v>453.1</v>
+        <v>461.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C29" t="n">
-        <v>388</v>
+        <v>443</v>
       </c>
       <c r="D29" t="n">
-        <v>438</v>
+        <v>393</v>
       </c>
       <c r="E29" t="n">
-        <v>393</v>
+        <v>463</v>
       </c>
       <c r="F29" t="n">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="G29" t="n">
+        <v>374</v>
+      </c>
+      <c r="H29" t="n">
         <v>406</v>
       </c>
-      <c r="H29" t="n">
-        <v>459</v>
-      </c>
       <c r="I29" t="n">
-        <v>415</v>
+        <v>508</v>
       </c>
       <c r="J29" t="n">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K29" t="n">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="L29" t="n">
-        <v>411.7</v>
+        <v>423.7</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>401</v>
+        <v>452</v>
       </c>
       <c r="C30" t="n">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="D30" t="n">
-        <v>384</v>
+        <v>465</v>
       </c>
       <c r="E30" t="n">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="F30" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
       <c r="G30" t="n">
-        <v>389</v>
+        <v>448</v>
       </c>
       <c r="H30" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="I30" t="n">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="J30" t="n">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="K30" t="n">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="L30" t="n">
-        <v>427.6</v>
+        <v>445.5</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>480</v>
+        <v>416</v>
       </c>
       <c r="C31" t="n">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D31" t="n">
-        <v>487</v>
+        <v>444</v>
       </c>
       <c r="E31" t="n">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="F31" t="n">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="G31" t="n">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="H31" t="n">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="I31" t="n">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="J31" t="n">
-        <v>485</v>
+        <v>426</v>
       </c>
       <c r="K31" t="n">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="L31" t="n">
-        <v>465.9</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
+        <v>432</v>
+      </c>
+      <c r="C32" t="n">
+        <v>419</v>
+      </c>
+      <c r="D32" t="n">
         <v>408</v>
       </c>
-      <c r="C32" t="n">
-        <v>423</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>421</v>
+      </c>
+      <c r="F32" t="n">
+        <v>418</v>
+      </c>
+      <c r="G32" t="n">
         <v>414</v>
       </c>
-      <c r="E32" t="n">
-        <v>428</v>
-      </c>
-      <c r="F32" t="n">
-        <v>393</v>
-      </c>
-      <c r="G32" t="n">
-        <v>444</v>
-      </c>
       <c r="H32" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I32" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="J32" t="n">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="K32" t="n">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="L32" t="n">
-        <v>418.1</v>
+        <v>421.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="C33" t="n">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="D33" t="n">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E33" t="n">
-        <v>379</v>
+        <v>425</v>
       </c>
       <c r="F33" t="n">
-        <v>465</v>
+        <v>390</v>
       </c>
       <c r="G33" t="n">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="H33" t="n">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="I33" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="J33" t="n">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="K33" t="n">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="L33" t="n">
-        <v>403.2</v>
+        <v>415</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>457</v>
+        <v>387</v>
       </c>
       <c r="C34" t="n">
-        <v>443</v>
+        <v>379</v>
       </c>
       <c r="D34" t="n">
-        <v>376</v>
+        <v>527</v>
       </c>
       <c r="E34" t="n">
-        <v>421</v>
+        <v>529</v>
       </c>
       <c r="F34" t="n">
-        <v>469</v>
+        <v>416</v>
       </c>
       <c r="G34" t="n">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="H34" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I34" t="n">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="J34" t="n">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="K34" t="n">
-        <v>435</v>
+        <v>393</v>
       </c>
       <c r="L34" t="n">
-        <v>429.9</v>
+        <v>434.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>496</v>
+        <v>447</v>
       </c>
       <c r="C35" t="n">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="D35" t="n">
+        <v>461</v>
+      </c>
+      <c r="E35" t="n">
+        <v>527</v>
+      </c>
+      <c r="F35" t="n">
+        <v>538</v>
+      </c>
+      <c r="G35" t="n">
+        <v>567</v>
+      </c>
+      <c r="H35" t="n">
+        <v>460</v>
+      </c>
+      <c r="I35" t="n">
         <v>473</v>
       </c>
-      <c r="E35" t="n">
-        <v>532</v>
-      </c>
-      <c r="F35" t="n">
-        <v>511</v>
-      </c>
-      <c r="G35" t="n">
-        <v>508</v>
-      </c>
-      <c r="H35" t="n">
-        <v>458</v>
-      </c>
-      <c r="I35" t="n">
-        <v>487</v>
-      </c>
       <c r="J35" t="n">
-        <v>490</v>
+        <v>444</v>
       </c>
       <c r="K35" t="n">
-        <v>451</v>
+        <v>497</v>
       </c>
       <c r="L35" t="n">
-        <v>483.4</v>
+        <v>486.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C36" t="n">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D36" t="n">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E36" t="n">
-        <v>349</v>
+        <v>442</v>
       </c>
       <c r="F36" t="n">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="G36" t="n">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="H36" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="I36" t="n">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="J36" t="n">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="K36" t="n">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="L36" t="n">
-        <v>364.4</v>
+        <v>376.2</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="C37" t="n">
-        <v>507</v>
+        <v>448</v>
       </c>
       <c r="D37" t="n">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="E37" t="n">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="F37" t="n">
-        <v>479</v>
+        <v>438</v>
       </c>
       <c r="G37" t="n">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="H37" t="n">
-        <v>457</v>
+        <v>395</v>
       </c>
       <c r="I37" t="n">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="J37" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K37" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="L37" t="n">
-        <v>466.1</v>
+        <v>443.3</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="C38" t="n">
-        <v>515</v>
+        <v>576</v>
       </c>
       <c r="D38" t="n">
-        <v>484</v>
+        <v>562</v>
       </c>
       <c r="E38" t="n">
-        <v>500</v>
+        <v>619</v>
       </c>
       <c r="F38" t="n">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="G38" t="n">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="H38" t="n">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="I38" t="n">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="J38" t="n">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="K38" t="n">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="L38" t="n">
-        <v>509.1</v>
+        <v>532.1</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>466</v>
+        <v>375</v>
       </c>
       <c r="C39" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D39" t="n">
+        <v>377</v>
+      </c>
+      <c r="E39" t="n">
         <v>422</v>
       </c>
-      <c r="E39" t="n">
-        <v>391</v>
-      </c>
       <c r="F39" t="n">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="G39" t="n">
-        <v>332</v>
+        <v>413</v>
       </c>
       <c r="H39" t="n">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="I39" t="n">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="J39" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K39" t="n">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="L39" t="n">
-        <v>401</v>
+        <v>397.7</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="C40" t="n">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="D40" t="n">
+        <v>475</v>
+      </c>
+      <c r="E40" t="n">
         <v>448</v>
       </c>
-      <c r="E40" t="n">
-        <v>446</v>
-      </c>
       <c r="F40" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G40" t="n">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="H40" t="n">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="I40" t="n">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="J40" t="n">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="K40" t="n">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="L40" t="n">
-        <v>448.4</v>
+        <v>455.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>511</v>
+        <v>418</v>
       </c>
       <c r="C41" t="n">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D41" t="n">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="E41" t="n">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="F41" t="n">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="G41" t="n">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="H41" t="n">
-        <v>503</v>
+        <v>551</v>
       </c>
       <c r="I41" t="n">
         <v>511</v>
       </c>
       <c r="J41" t="n">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K41" t="n">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="L41" t="n">
-        <v>505</v>
+        <v>485.8</v>
       </c>
     </row>
     <row r="42">
@@ -1991,34 +1991,34 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
+        <v>469</v>
+      </c>
+      <c r="C42" t="n">
+        <v>445</v>
+      </c>
+      <c r="D42" t="n">
+        <v>424</v>
+      </c>
+      <c r="E42" t="n">
+        <v>469</v>
+      </c>
+      <c r="F42" t="n">
+        <v>461</v>
+      </c>
+      <c r="G42" t="n">
+        <v>472</v>
+      </c>
+      <c r="H42" t="n">
         <v>468</v>
       </c>
-      <c r="C42" t="n">
-        <v>416</v>
-      </c>
-      <c r="D42" t="n">
+      <c r="I42" t="n">
+        <v>451</v>
+      </c>
+      <c r="J42" t="n">
+        <v>464</v>
+      </c>
+      <c r="K42" t="n">
         <v>425</v>
-      </c>
-      <c r="E42" t="n">
-        <v>425</v>
-      </c>
-      <c r="F42" t="n">
-        <v>454</v>
-      </c>
-      <c r="G42" t="n">
-        <v>496</v>
-      </c>
-      <c r="H42" t="n">
-        <v>476</v>
-      </c>
-      <c r="I42" t="n">
-        <v>484</v>
-      </c>
-      <c r="J42" t="n">
-        <v>429</v>
-      </c>
-      <c r="K42" t="n">
-        <v>475</v>
       </c>
       <c r="L42" t="n">
         <v>454.8</v>
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="C43" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D43" t="n">
+        <v>461</v>
+      </c>
+      <c r="E43" t="n">
+        <v>446</v>
+      </c>
+      <c r="F43" t="n">
+        <v>434</v>
+      </c>
+      <c r="G43" t="n">
+        <v>455</v>
+      </c>
+      <c r="H43" t="n">
+        <v>500</v>
+      </c>
+      <c r="I43" t="n">
         <v>485</v>
       </c>
-      <c r="E43" t="n">
-        <v>452</v>
-      </c>
-      <c r="F43" t="n">
-        <v>451</v>
-      </c>
-      <c r="G43" t="n">
-        <v>484</v>
-      </c>
-      <c r="H43" t="n">
-        <v>432</v>
-      </c>
-      <c r="I43" t="n">
-        <v>453</v>
-      </c>
       <c r="J43" t="n">
-        <v>449</v>
+        <v>388</v>
       </c>
       <c r="K43" t="n">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="L43" t="n">
-        <v>457.4</v>
+        <v>449.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="C44" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D44" t="n">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E44" t="n">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="F44" t="n">
-        <v>445</v>
+        <v>527</v>
       </c>
       <c r="G44" t="n">
-        <v>447</v>
+        <v>491</v>
       </c>
       <c r="H44" t="n">
-        <v>507</v>
+        <v>433</v>
       </c>
       <c r="I44" t="n">
-        <v>444</v>
+        <v>511</v>
       </c>
       <c r="J44" t="n">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="K44" t="n">
-        <v>458</v>
+        <v>517</v>
       </c>
       <c r="L44" t="n">
-        <v>446.3</v>
+        <v>464.8</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>470</v>
+        <v>548</v>
       </c>
       <c r="C45" t="n">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="D45" t="n">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="E45" t="n">
-        <v>524</v>
+        <v>424</v>
       </c>
       <c r="F45" t="n">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="G45" t="n">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="H45" t="n">
-        <v>393</v>
+        <v>510</v>
       </c>
       <c r="I45" t="n">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="J45" t="n">
-        <v>460</v>
+        <v>386</v>
       </c>
       <c r="K45" t="n">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="L45" t="n">
-        <v>471</v>
+        <v>470.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
+        <v>370</v>
+      </c>
+      <c r="C46" t="n">
+        <v>385</v>
+      </c>
+      <c r="D46" t="n">
         <v>373</v>
       </c>
-      <c r="C46" t="n">
-        <v>372</v>
-      </c>
-      <c r="D46" t="n">
-        <v>374</v>
-      </c>
       <c r="E46" t="n">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="F46" t="n">
-        <v>349</v>
+        <v>410</v>
       </c>
       <c r="G46" t="n">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="H46" t="n">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="I46" t="n">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="J46" t="n">
-        <v>390</v>
+        <v>432</v>
       </c>
       <c r="K46" t="n">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="L46" t="n">
-        <v>382.7</v>
+        <v>402.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="C47" t="n">
-        <v>543</v>
+        <v>491</v>
       </c>
       <c r="D47" t="n">
-        <v>578</v>
+        <v>481</v>
       </c>
       <c r="E47" t="n">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="F47" t="n">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="G47" t="n">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="H47" t="n">
-        <v>570</v>
+        <v>526</v>
       </c>
       <c r="I47" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="J47" t="n">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="K47" t="n">
-        <v>530</v>
+        <v>493</v>
       </c>
       <c r="L47" t="n">
-        <v>517.3</v>
+        <v>489.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>500</v>
+        <v>464</v>
       </c>
       <c r="C48" t="n">
-        <v>505</v>
+        <v>456</v>
       </c>
       <c r="D48" t="n">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="E48" t="n">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="F48" t="n">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="G48" t="n">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="H48" t="n">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="I48" t="n">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="J48" t="n">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="K48" t="n">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="L48" t="n">
-        <v>486.6</v>
+        <v>461.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="C49" t="n">
-        <v>504</v>
+        <v>417</v>
       </c>
       <c r="D49" t="n">
-        <v>412</v>
+        <v>523</v>
       </c>
       <c r="E49" t="n">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="F49" t="n">
-        <v>414</v>
+        <v>489</v>
       </c>
       <c r="G49" t="n">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="H49" t="n">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="I49" t="n">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="J49" t="n">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="K49" t="n">
-        <v>441</v>
+        <v>385</v>
       </c>
       <c r="L49" t="n">
-        <v>438.9</v>
+        <v>449.3</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
+        <v>448</v>
+      </c>
+      <c r="C50" t="n">
+        <v>396</v>
+      </c>
+      <c r="D50" t="n">
+        <v>390</v>
+      </c>
+      <c r="E50" t="n">
+        <v>439</v>
+      </c>
+      <c r="F50" t="n">
+        <v>402</v>
+      </c>
+      <c r="G50" t="n">
+        <v>442</v>
+      </c>
+      <c r="H50" t="n">
+        <v>418</v>
+      </c>
+      <c r="I50" t="n">
         <v>474</v>
       </c>
-      <c r="C50" t="n">
-        <v>408</v>
-      </c>
-      <c r="D50" t="n">
-        <v>395</v>
-      </c>
-      <c r="E50" t="n">
-        <v>414</v>
-      </c>
-      <c r="F50" t="n">
-        <v>456</v>
-      </c>
-      <c r="G50" t="n">
-        <v>404</v>
-      </c>
-      <c r="H50" t="n">
-        <v>414</v>
-      </c>
-      <c r="I50" t="n">
-        <v>426</v>
-      </c>
       <c r="J50" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K50" t="n">
-        <v>409</v>
+        <v>499</v>
       </c>
       <c r="L50" t="n">
-        <v>423.3</v>
+        <v>434</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="C51" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D51" t="n">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="E51" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F51" t="n">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="G51" t="n">
-        <v>417</v>
+        <v>462</v>
       </c>
       <c r="H51" t="n">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="I51" t="n">
-        <v>447</v>
+        <v>368</v>
       </c>
       <c r="J51" t="n">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="K51" t="n">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="L51" t="n">
-        <v>417</v>
+        <v>417.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>465.26</v>
+        <v>455.52</v>
       </c>
       <c r="C52" t="n">
-        <v>458.08</v>
+        <v>462.5</v>
       </c>
       <c r="D52" t="n">
-        <v>457.5</v>
+        <v>458.44</v>
       </c>
       <c r="E52" t="n">
-        <v>455.88</v>
+        <v>465.98</v>
       </c>
       <c r="F52" t="n">
-        <v>463.52</v>
+        <v>456.12</v>
       </c>
       <c r="G52" t="n">
-        <v>458.08</v>
+        <v>461.34</v>
       </c>
       <c r="H52" t="n">
-        <v>454.62</v>
+        <v>456.72</v>
       </c>
       <c r="I52" t="n">
-        <v>459.26</v>
+        <v>459.5</v>
       </c>
       <c r="J52" t="n">
-        <v>456.32</v>
+        <v>458.28</v>
       </c>
       <c r="K52" t="n">
-        <v>461.32</v>
+        <v>458.96</v>
       </c>
       <c r="L52" t="n">
-        <v>458.984</v>
+        <v>459.336</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.481838464736938</v>
+        <v>2.28577733039856</v>
       </c>
       <c r="C2" t="n">
-        <v>2.35097336769104</v>
+        <v>2.399077653884888</v>
       </c>
       <c r="D2" t="n">
-        <v>2.032776355743408</v>
+        <v>2.459910154342651</v>
       </c>
       <c r="E2" t="n">
-        <v>2.226196050643921</v>
+        <v>2.320720195770264</v>
       </c>
       <c r="F2" t="n">
-        <v>2.446933507919312</v>
+        <v>2.38067889213562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.387273073196411</v>
+        <v>2.173941135406494</v>
       </c>
       <c r="H2" t="n">
-        <v>2.289166212081909</v>
+        <v>2.266906023025513</v>
       </c>
       <c r="I2" t="n">
-        <v>3.357771873474121</v>
+        <v>2.30861234664917</v>
       </c>
       <c r="J2" t="n">
-        <v>2.495062589645386</v>
+        <v>2.352717638015747</v>
       </c>
       <c r="K2" t="n">
-        <v>2.314865350723267</v>
+        <v>2.334160089492798</v>
       </c>
       <c r="L2" t="n">
-        <v>2.438285684585571</v>
+        <v>2.32825014591217</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.558606147766113</v>
+        <v>2.399237155914307</v>
       </c>
       <c r="C3" t="n">
-        <v>2.428601264953613</v>
+        <v>2.255566835403442</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5217604637146</v>
+        <v>2.516692876815796</v>
       </c>
       <c r="E3" t="n">
-        <v>2.700114250183105</v>
+        <v>2.344861268997192</v>
       </c>
       <c r="F3" t="n">
-        <v>2.514559745788574</v>
+        <v>2.46714973449707</v>
       </c>
       <c r="G3" t="n">
-        <v>2.949136734008789</v>
+        <v>2.678568363189697</v>
       </c>
       <c r="H3" t="n">
-        <v>2.37436580657959</v>
+        <v>2.586158752441406</v>
       </c>
       <c r="I3" t="n">
-        <v>2.526689052581787</v>
+        <v>2.372047662734985</v>
       </c>
       <c r="J3" t="n">
-        <v>2.206365585327148</v>
+        <v>2.573128223419189</v>
       </c>
       <c r="K3" t="n">
-        <v>2.803683519363403</v>
+        <v>2.469143152236938</v>
       </c>
       <c r="L3" t="n">
-        <v>2.558388257026672</v>
+        <v>2.466255402565003</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.447682619094849</v>
+        <v>2.52296781539917</v>
       </c>
       <c r="C4" t="n">
-        <v>2.463703632354736</v>
+        <v>2.614563703536987</v>
       </c>
       <c r="D4" t="n">
-        <v>2.484730958938599</v>
+        <v>2.54626202583313</v>
       </c>
       <c r="E4" t="n">
-        <v>2.467223405838013</v>
+        <v>2.559996128082275</v>
       </c>
       <c r="F4" t="n">
-        <v>2.252129793167114</v>
+        <v>2.449285984039307</v>
       </c>
       <c r="G4" t="n">
-        <v>2.376773834228516</v>
+        <v>2.462248802185059</v>
       </c>
       <c r="H4" t="n">
-        <v>2.362356185913086</v>
+        <v>2.483849287033081</v>
       </c>
       <c r="I4" t="n">
-        <v>2.328456163406372</v>
+        <v>2.666272163391113</v>
       </c>
       <c r="J4" t="n">
-        <v>2.87232494354248</v>
+        <v>2.530943870544434</v>
       </c>
       <c r="K4" t="n">
-        <v>2.605544567108154</v>
+        <v>2.485586404800415</v>
       </c>
       <c r="L4" t="n">
-        <v>2.466092610359192</v>
+        <v>2.532197618484497</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.099108457565308</v>
+        <v>2.177228927612305</v>
       </c>
       <c r="C5" t="n">
-        <v>2.163207292556763</v>
+        <v>2.311924695968628</v>
       </c>
       <c r="D5" t="n">
-        <v>2.156779289245605</v>
+        <v>2.134793758392334</v>
       </c>
       <c r="E5" t="n">
-        <v>2.093379259109497</v>
+        <v>2.294657230377197</v>
       </c>
       <c r="F5" t="n">
-        <v>2.131028175354004</v>
+        <v>2.224644184112549</v>
       </c>
       <c r="G5" t="n">
-        <v>2.098146438598633</v>
+        <v>2.295087814331055</v>
       </c>
       <c r="H5" t="n">
-        <v>2.158803701400757</v>
+        <v>2.22988748550415</v>
       </c>
       <c r="I5" t="n">
-        <v>2.334809303283691</v>
+        <v>2.369951963424683</v>
       </c>
       <c r="J5" t="n">
-        <v>2.260248422622681</v>
+        <v>2.469135999679565</v>
       </c>
       <c r="K5" t="n">
-        <v>2.11748194694519</v>
+        <v>2.347871541976929</v>
       </c>
       <c r="L5" t="n">
-        <v>2.161299228668213</v>
+        <v>2.28551836013794</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.12937068939209</v>
+        <v>2.046921968460083</v>
       </c>
       <c r="C6" t="n">
-        <v>1.865311145782471</v>
+        <v>2.218756914138794</v>
       </c>
       <c r="D6" t="n">
-        <v>1.963126182556152</v>
+        <v>2.39473032951355</v>
       </c>
       <c r="E6" t="n">
-        <v>1.911666870117188</v>
+        <v>2.032503366470337</v>
       </c>
       <c r="F6" t="n">
-        <v>2.070623874664307</v>
+        <v>2.056983232498169</v>
       </c>
       <c r="G6" t="n">
-        <v>1.899420022964478</v>
+        <v>2.103329181671143</v>
       </c>
       <c r="H6" t="n">
-        <v>1.963062524795532</v>
+        <v>1.949287176132202</v>
       </c>
       <c r="I6" t="n">
-        <v>2.030473709106445</v>
+        <v>2.270352602005005</v>
       </c>
       <c r="J6" t="n">
-        <v>1.994786500930786</v>
+        <v>2.229548931121826</v>
       </c>
       <c r="K6" t="n">
-        <v>1.904114007949829</v>
+        <v>2.302051544189453</v>
       </c>
       <c r="L6" t="n">
-        <v>1.973195552825928</v>
+        <v>2.160446524620056</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.376506090164185</v>
+        <v>2.375665903091431</v>
       </c>
       <c r="C7" t="n">
-        <v>2.423938512802124</v>
+        <v>2.396130323410034</v>
       </c>
       <c r="D7" t="n">
-        <v>2.311093330383301</v>
+        <v>2.294240474700928</v>
       </c>
       <c r="E7" t="n">
-        <v>2.286330699920654</v>
+        <v>2.630089282989502</v>
       </c>
       <c r="F7" t="n">
-        <v>2.43621301651001</v>
+        <v>2.428927183151245</v>
       </c>
       <c r="G7" t="n">
-        <v>2.634380340576172</v>
+        <v>2.396941661834717</v>
       </c>
       <c r="H7" t="n">
-        <v>2.540520429611206</v>
+        <v>2.503365516662598</v>
       </c>
       <c r="I7" t="n">
-        <v>2.275363206863403</v>
+        <v>2.416126728057861</v>
       </c>
       <c r="J7" t="n">
-        <v>2.377439260482788</v>
+        <v>2.388539791107178</v>
       </c>
       <c r="K7" t="n">
-        <v>2.406560897827148</v>
+        <v>2.421058654785156</v>
       </c>
       <c r="L7" t="n">
-        <v>2.406834578514099</v>
+        <v>2.425108551979065</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.473113536834717</v>
+        <v>2.539770364761353</v>
       </c>
       <c r="C8" t="n">
-        <v>2.388509750366211</v>
+        <v>2.380146503448486</v>
       </c>
       <c r="D8" t="n">
-        <v>2.262839078903198</v>
+        <v>2.554821968078613</v>
       </c>
       <c r="E8" t="n">
-        <v>2.326034784317017</v>
+        <v>2.537305355072021</v>
       </c>
       <c r="F8" t="n">
-        <v>2.481148958206177</v>
+        <v>2.531856536865234</v>
       </c>
       <c r="G8" t="n">
-        <v>2.286735057830811</v>
+        <v>2.526954889297485</v>
       </c>
       <c r="H8" t="n">
-        <v>2.360754489898682</v>
+        <v>2.71251106262207</v>
       </c>
       <c r="I8" t="n">
-        <v>2.281781196594238</v>
+        <v>2.416687488555908</v>
       </c>
       <c r="J8" t="n">
-        <v>2.505493640899658</v>
+        <v>2.554023265838623</v>
       </c>
       <c r="K8" t="n">
-        <v>2.405193090438843</v>
+        <v>2.508271455764771</v>
       </c>
       <c r="L8" t="n">
-        <v>2.377160358428955</v>
+        <v>2.526234889030456</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.521698951721191</v>
+        <v>2.400147438049316</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2196044921875</v>
+        <v>2.343737602233887</v>
       </c>
       <c r="D9" t="n">
-        <v>2.27721643447876</v>
+        <v>2.266353130340576</v>
       </c>
       <c r="E9" t="n">
-        <v>2.110221385955811</v>
+        <v>2.326498031616211</v>
       </c>
       <c r="F9" t="n">
-        <v>2.31982421875</v>
+        <v>2.357869863510132</v>
       </c>
       <c r="G9" t="n">
-        <v>2.219577312469482</v>
+        <v>2.213055372238159</v>
       </c>
       <c r="H9" t="n">
-        <v>2.226658821105957</v>
+        <v>2.683606863021851</v>
       </c>
       <c r="I9" t="n">
-        <v>2.269465923309326</v>
+        <v>2.505082130432129</v>
       </c>
       <c r="J9" t="n">
-        <v>2.319703340530396</v>
+        <v>2.355518102645874</v>
       </c>
       <c r="K9" t="n">
-        <v>2.238006114959717</v>
+        <v>2.393857479095459</v>
       </c>
       <c r="L9" t="n">
-        <v>2.272197699546814</v>
+        <v>2.384572601318359</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.270025730133057</v>
+        <v>2.235582590103149</v>
       </c>
       <c r="C10" t="n">
-        <v>2.446648359298706</v>
+        <v>2.349132299423218</v>
       </c>
       <c r="D10" t="n">
-        <v>2.500869989395142</v>
+        <v>2.472821474075317</v>
       </c>
       <c r="E10" t="n">
-        <v>2.209563970565796</v>
+        <v>2.684008598327637</v>
       </c>
       <c r="F10" t="n">
-        <v>2.192966461181641</v>
+        <v>2.358186721801758</v>
       </c>
       <c r="G10" t="n">
-        <v>2.20341682434082</v>
+        <v>2.469582080841064</v>
       </c>
       <c r="H10" t="n">
-        <v>2.307306528091431</v>
+        <v>2.460397958755493</v>
       </c>
       <c r="I10" t="n">
-        <v>2.263896465301514</v>
+        <v>2.517999410629272</v>
       </c>
       <c r="J10" t="n">
-        <v>2.300504446029663</v>
+        <v>2.287834405899048</v>
       </c>
       <c r="K10" t="n">
-        <v>2.21389102935791</v>
+        <v>2.392139434814453</v>
       </c>
       <c r="L10" t="n">
-        <v>2.290908980369568</v>
+        <v>2.422768497467041</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1.93795919418335</v>
+        <v>2.130014657974243</v>
       </c>
       <c r="C11" t="n">
-        <v>2.078396081924438</v>
+        <v>2.191169500350952</v>
       </c>
       <c r="D11" t="n">
-        <v>1.910085201263428</v>
+        <v>2.101079702377319</v>
       </c>
       <c r="E11" t="n">
-        <v>1.95297384262085</v>
+        <v>2.215917348861694</v>
       </c>
       <c r="F11" t="n">
-        <v>2.014410972595215</v>
+        <v>2.19084620475769</v>
       </c>
       <c r="G11" t="n">
-        <v>2.004970073699951</v>
+        <v>2.019073963165283</v>
       </c>
       <c r="H11" t="n">
-        <v>1.950968503952026</v>
+        <v>2.068012714385986</v>
       </c>
       <c r="I11" t="n">
-        <v>2.07471752166748</v>
+        <v>2.145161867141724</v>
       </c>
       <c r="J11" t="n">
-        <v>1.909624814987183</v>
+        <v>2.01461386680603</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08493971824646</v>
+        <v>2.209927082061768</v>
       </c>
       <c r="L11" t="n">
-        <v>1.991904592514038</v>
+        <v>2.128581690788269</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.228042364120483</v>
+        <v>2.508877754211426</v>
       </c>
       <c r="C12" t="n">
-        <v>2.348530530929565</v>
+        <v>2.643166303634644</v>
       </c>
       <c r="D12" t="n">
-        <v>2.247231483459473</v>
+        <v>2.394051313400269</v>
       </c>
       <c r="E12" t="n">
-        <v>2.353395938873291</v>
+        <v>2.658761501312256</v>
       </c>
       <c r="F12" t="n">
-        <v>2.213131904602051</v>
+        <v>2.52269434928894</v>
       </c>
       <c r="G12" t="n">
-        <v>2.146515607833862</v>
+        <v>2.455479860305786</v>
       </c>
       <c r="H12" t="n">
-        <v>2.27718710899353</v>
+        <v>2.569684505462646</v>
       </c>
       <c r="I12" t="n">
-        <v>2.162987947463989</v>
+        <v>2.280805826187134</v>
       </c>
       <c r="J12" t="n">
-        <v>2.285318374633789</v>
+        <v>2.257907629013062</v>
       </c>
       <c r="K12" t="n">
-        <v>2.394644260406494</v>
+        <v>2.528508901596069</v>
       </c>
       <c r="L12" t="n">
-        <v>2.265698552131653</v>
+        <v>2.481993794441223</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.300289869308472</v>
+        <v>2.675493001937866</v>
       </c>
       <c r="C13" t="n">
-        <v>2.324817657470703</v>
+        <v>2.468705177307129</v>
       </c>
       <c r="D13" t="n">
-        <v>2.290022373199463</v>
+        <v>2.378942489624023</v>
       </c>
       <c r="E13" t="n">
-        <v>2.223910808563232</v>
+        <v>2.592492818832397</v>
       </c>
       <c r="F13" t="n">
-        <v>2.439083337783813</v>
+        <v>2.436773777008057</v>
       </c>
       <c r="G13" t="n">
-        <v>2.339221000671387</v>
+        <v>2.31729531288147</v>
       </c>
       <c r="H13" t="n">
-        <v>2.263112783432007</v>
+        <v>2.561895608901978</v>
       </c>
       <c r="I13" t="n">
-        <v>2.191843032836914</v>
+        <v>2.527018785476685</v>
       </c>
       <c r="J13" t="n">
-        <v>2.431987047195435</v>
+        <v>2.554697275161743</v>
       </c>
       <c r="K13" t="n">
-        <v>2.281279802322388</v>
+        <v>2.413429021835327</v>
       </c>
       <c r="L13" t="n">
-        <v>2.308556771278381</v>
+        <v>2.492674326896668</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.626334190368652</v>
+        <v>2.509079456329346</v>
       </c>
       <c r="C14" t="n">
-        <v>2.288229942321777</v>
+        <v>2.67537260055542</v>
       </c>
       <c r="D14" t="n">
-        <v>2.349491596221924</v>
+        <v>2.301143169403076</v>
       </c>
       <c r="E14" t="n">
-        <v>2.618671655654907</v>
+        <v>2.49858283996582</v>
       </c>
       <c r="F14" t="n">
-        <v>2.405611991882324</v>
+        <v>2.539408683776855</v>
       </c>
       <c r="G14" t="n">
-        <v>2.386385917663574</v>
+        <v>2.571293592453003</v>
       </c>
       <c r="H14" t="n">
-        <v>2.581520795822144</v>
+        <v>2.666096925735474</v>
       </c>
       <c r="I14" t="n">
-        <v>2.468563556671143</v>
+        <v>2.548866987228394</v>
       </c>
       <c r="J14" t="n">
-        <v>2.621468305587769</v>
+        <v>2.459221839904785</v>
       </c>
       <c r="K14" t="n">
-        <v>2.51230001449585</v>
+        <v>2.504550218582153</v>
       </c>
       <c r="L14" t="n">
-        <v>2.485857796669007</v>
+        <v>2.527361631393433</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.163744926452637</v>
+        <v>2.290947437286377</v>
       </c>
       <c r="C15" t="n">
-        <v>2.069146633148193</v>
+        <v>2.374468326568604</v>
       </c>
       <c r="D15" t="n">
-        <v>2.230927705764771</v>
+        <v>2.386114835739136</v>
       </c>
       <c r="E15" t="n">
-        <v>2.174380302429199</v>
+        <v>2.382911205291748</v>
       </c>
       <c r="F15" t="n">
-        <v>2.315977573394775</v>
+        <v>2.333470582962036</v>
       </c>
       <c r="G15" t="n">
-        <v>2.184163331985474</v>
+        <v>2.143460988998413</v>
       </c>
       <c r="H15" t="n">
-        <v>2.191950798034668</v>
+        <v>2.21481466293335</v>
       </c>
       <c r="I15" t="n">
-        <v>2.283258438110352</v>
+        <v>2.347272157669067</v>
       </c>
       <c r="J15" t="n">
-        <v>2.168699741363525</v>
+        <v>2.269204139709473</v>
       </c>
       <c r="K15" t="n">
-        <v>2.107268571853638</v>
+        <v>2.282793283462524</v>
       </c>
       <c r="L15" t="n">
-        <v>2.188951802253723</v>
+        <v>2.302545762062073</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.293911218643188</v>
+        <v>2.423701047897339</v>
       </c>
       <c r="C16" t="n">
-        <v>2.285222768783569</v>
+        <v>2.48682689666748</v>
       </c>
       <c r="D16" t="n">
-        <v>2.252140998840332</v>
+        <v>2.403191328048706</v>
       </c>
       <c r="E16" t="n">
-        <v>2.260935306549072</v>
+        <v>2.427658557891846</v>
       </c>
       <c r="F16" t="n">
-        <v>2.25673770904541</v>
+        <v>2.32565450668335</v>
       </c>
       <c r="G16" t="n">
-        <v>2.331709146499634</v>
+        <v>2.261949062347412</v>
       </c>
       <c r="H16" t="n">
-        <v>2.380081415176392</v>
+        <v>2.414136409759521</v>
       </c>
       <c r="I16" t="n">
-        <v>2.313185930252075</v>
+        <v>2.523214340209961</v>
       </c>
       <c r="J16" t="n">
-        <v>2.385072946548462</v>
+        <v>2.676649332046509</v>
       </c>
       <c r="K16" t="n">
-        <v>2.279927492141724</v>
+        <v>2.33944034576416</v>
       </c>
       <c r="L16" t="n">
-        <v>2.303892493247986</v>
+        <v>2.428242182731629</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.489005565643311</v>
+        <v>2.281927108764648</v>
       </c>
       <c r="C17" t="n">
-        <v>2.22137188911438</v>
+        <v>2.373985052108765</v>
       </c>
       <c r="D17" t="n">
-        <v>2.061348915100098</v>
+        <v>2.525486707687378</v>
       </c>
       <c r="E17" t="n">
-        <v>2.116692543029785</v>
+        <v>2.352049827575684</v>
       </c>
       <c r="F17" t="n">
-        <v>2.063288450241089</v>
+        <v>2.367624759674072</v>
       </c>
       <c r="G17" t="n">
-        <v>2.416804075241089</v>
+        <v>2.426955699920654</v>
       </c>
       <c r="H17" t="n">
-        <v>1.938694953918457</v>
+        <v>2.40242600440979</v>
       </c>
       <c r="I17" t="n">
-        <v>2.263053417205811</v>
+        <v>2.218669891357422</v>
       </c>
       <c r="J17" t="n">
-        <v>2.114517211914062</v>
+        <v>2.117833375930786</v>
       </c>
       <c r="K17" t="n">
-        <v>2.357535600662231</v>
+        <v>3.642764329910278</v>
       </c>
       <c r="L17" t="n">
-        <v>2.204231262207031</v>
+        <v>2.470972275733948</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.587466955184937</v>
+        <v>2.62318229675293</v>
       </c>
       <c r="C18" t="n">
-        <v>2.542726039886475</v>
+        <v>2.308501243591309</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2677903175354</v>
+        <v>2.504989862442017</v>
       </c>
       <c r="E18" t="n">
-        <v>2.45427417755127</v>
+        <v>2.405731916427612</v>
       </c>
       <c r="F18" t="n">
-        <v>2.487120866775513</v>
+        <v>2.329457759857178</v>
       </c>
       <c r="G18" t="n">
-        <v>2.376991987228394</v>
+        <v>2.321961641311646</v>
       </c>
       <c r="H18" t="n">
-        <v>2.462321996688843</v>
+        <v>2.470570802688599</v>
       </c>
       <c r="I18" t="n">
-        <v>2.437898397445679</v>
+        <v>2.456117630004883</v>
       </c>
       <c r="J18" t="n">
-        <v>2.455443859100342</v>
+        <v>2.494005441665649</v>
       </c>
       <c r="K18" t="n">
-        <v>2.837525367736816</v>
+        <v>2.488023042678833</v>
       </c>
       <c r="L18" t="n">
-        <v>2.490955996513367</v>
+        <v>2.440254163742066</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.351391553878784</v>
+        <v>2.287540674209595</v>
       </c>
       <c r="C19" t="n">
-        <v>2.317231893539429</v>
+        <v>2.127957105636597</v>
       </c>
       <c r="D19" t="n">
-        <v>2.294554471969604</v>
+        <v>2.388782024383545</v>
       </c>
       <c r="E19" t="n">
-        <v>2.214912891387939</v>
+        <v>2.300501823425293</v>
       </c>
       <c r="F19" t="n">
-        <v>2.338570594787598</v>
+        <v>2.265095472335815</v>
       </c>
       <c r="G19" t="n">
-        <v>2.337259769439697</v>
+        <v>2.050154447555542</v>
       </c>
       <c r="H19" t="n">
-        <v>2.440148591995239</v>
+        <v>2.35935115814209</v>
       </c>
       <c r="I19" t="n">
-        <v>2.273160219192505</v>
+        <v>2.488036870956421</v>
       </c>
       <c r="J19" t="n">
-        <v>2.198753595352173</v>
+        <v>2.424688100814819</v>
       </c>
       <c r="K19" t="n">
-        <v>2.296646118164062</v>
+        <v>2.356879949569702</v>
       </c>
       <c r="L19" t="n">
-        <v>2.306262969970703</v>
+        <v>2.304898762702942</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.217373132705688</v>
+        <v>2.378802299499512</v>
       </c>
       <c r="C20" t="n">
-        <v>2.310027360916138</v>
+        <v>2.238174438476562</v>
       </c>
       <c r="D20" t="n">
-        <v>2.263990879058838</v>
+        <v>2.369825124740601</v>
       </c>
       <c r="E20" t="n">
-        <v>2.241704940795898</v>
+        <v>2.070600748062134</v>
       </c>
       <c r="F20" t="n">
-        <v>2.496571063995361</v>
+        <v>2.168354511260986</v>
       </c>
       <c r="G20" t="n">
-        <v>2.40536642074585</v>
+        <v>2.313475370407104</v>
       </c>
       <c r="H20" t="n">
-        <v>2.379287481307983</v>
+        <v>2.255130529403687</v>
       </c>
       <c r="I20" t="n">
-        <v>2.247331142425537</v>
+        <v>2.249675989151001</v>
       </c>
       <c r="J20" t="n">
-        <v>2.102434158325195</v>
+        <v>2.098066568374634</v>
       </c>
       <c r="K20" t="n">
-        <v>2.073281526565552</v>
+        <v>2.357385158538818</v>
       </c>
       <c r="L20" t="n">
-        <v>2.273736810684204</v>
+        <v>2.249949073791504</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.295660018920898</v>
+        <v>2.352880477905273</v>
       </c>
       <c r="C21" t="n">
-        <v>2.241274118423462</v>
+        <v>2.369824409484863</v>
       </c>
       <c r="D21" t="n">
-        <v>2.306926250457764</v>
+        <v>2.490507841110229</v>
       </c>
       <c r="E21" t="n">
-        <v>2.286475419998169</v>
+        <v>2.477043628692627</v>
       </c>
       <c r="F21" t="n">
-        <v>2.293287992477417</v>
+        <v>2.370846509933472</v>
       </c>
       <c r="G21" t="n">
-        <v>2.309564352035522</v>
+        <v>2.428677558898926</v>
       </c>
       <c r="H21" t="n">
-        <v>2.330690383911133</v>
+        <v>2.217218637466431</v>
       </c>
       <c r="I21" t="n">
-        <v>2.192591667175293</v>
+        <v>2.259625434875488</v>
       </c>
       <c r="J21" t="n">
-        <v>3.670011043548584</v>
+        <v>2.37231969833374</v>
       </c>
       <c r="K21" t="n">
-        <v>2.364473581314087</v>
+        <v>2.469065189361572</v>
       </c>
       <c r="L21" t="n">
-        <v>2.429095482826233</v>
+        <v>2.380800938606262</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.112372159957886</v>
+        <v>2.209242343902588</v>
       </c>
       <c r="C22" t="n">
-        <v>2.205896854400635</v>
+        <v>2.265605449676514</v>
       </c>
       <c r="D22" t="n">
-        <v>2.076191663742065</v>
+        <v>2.390780687332153</v>
       </c>
       <c r="E22" t="n">
-        <v>2.187032699584961</v>
+        <v>2.419502973556519</v>
       </c>
       <c r="F22" t="n">
-        <v>2.240876913070679</v>
+        <v>2.193417072296143</v>
       </c>
       <c r="G22" t="n">
-        <v>2.127465724945068</v>
+        <v>2.216352462768555</v>
       </c>
       <c r="H22" t="n">
-        <v>2.439639091491699</v>
+        <v>2.307609796524048</v>
       </c>
       <c r="I22" t="n">
-        <v>2.488193035125732</v>
+        <v>2.204367399215698</v>
       </c>
       <c r="J22" t="n">
-        <v>2.322077512741089</v>
+        <v>2.309607982635498</v>
       </c>
       <c r="K22" t="n">
-        <v>2.249900579452515</v>
+        <v>2.177459001541138</v>
       </c>
       <c r="L22" t="n">
-        <v>2.244964623451233</v>
+        <v>2.269394516944885</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>2.130285263061523</v>
+        <v>1.990923166275024</v>
       </c>
       <c r="C23" t="n">
-        <v>2.111364126205444</v>
+        <v>2.003907442092896</v>
       </c>
       <c r="D23" t="n">
-        <v>2.130579233169556</v>
+        <v>2.092654466629028</v>
       </c>
       <c r="E23" t="n">
-        <v>2.016284227371216</v>
+        <v>2.078219890594482</v>
       </c>
       <c r="F23" t="n">
-        <v>2.075242757797241</v>
+        <v>2.02595043182373</v>
       </c>
       <c r="G23" t="n">
-        <v>2.033784151077271</v>
+        <v>1.993805646896362</v>
       </c>
       <c r="H23" t="n">
-        <v>1.961357593536377</v>
+        <v>2.006787776947021</v>
       </c>
       <c r="I23" t="n">
-        <v>2.238072156906128</v>
+        <v>2.00876259803772</v>
       </c>
       <c r="J23" t="n">
-        <v>1.990694522857666</v>
+        <v>2.058141946792603</v>
       </c>
       <c r="K23" t="n">
-        <v>2.026027679443359</v>
+        <v>2.190303802490234</v>
       </c>
       <c r="L23" t="n">
-        <v>2.071369171142578</v>
+        <v>2.04494571685791</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>2.155176877975464</v>
+        <v>2.101022481918335</v>
       </c>
       <c r="C24" t="n">
-        <v>1.974953889846802</v>
+        <v>2.123974323272705</v>
       </c>
       <c r="D24" t="n">
-        <v>2.052209615707397</v>
+        <v>2.018740653991699</v>
       </c>
       <c r="E24" t="n">
-        <v>2.091621398925781</v>
+        <v>2.027716159820557</v>
       </c>
       <c r="F24" t="n">
-        <v>2.037372350692749</v>
+        <v>2.064121961593628</v>
       </c>
       <c r="G24" t="n">
-        <v>2.037365913391113</v>
+        <v>2.189311504364014</v>
       </c>
       <c r="H24" t="n">
-        <v>2.189129829406738</v>
+        <v>1.970863103866577</v>
       </c>
       <c r="I24" t="n">
-        <v>2.022597312927246</v>
+        <v>2.164858341217041</v>
       </c>
       <c r="J24" t="n">
-        <v>2.080521106719971</v>
+        <v>2.100050687789917</v>
       </c>
       <c r="K24" t="n">
-        <v>2.12356162071228</v>
+        <v>2.017743825912476</v>
       </c>
       <c r="L24" t="n">
-        <v>2.076450991630554</v>
+        <v>2.077840304374695</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.030592441558838</v>
+        <v>2.29454231262207</v>
       </c>
       <c r="C25" t="n">
-        <v>2.29547905921936</v>
+        <v>2.372821807861328</v>
       </c>
       <c r="D25" t="n">
-        <v>2.254955291748047</v>
+        <v>2.184313535690308</v>
       </c>
       <c r="E25" t="n">
-        <v>2.282926321029663</v>
+        <v>2.044974803924561</v>
       </c>
       <c r="F25" t="n">
-        <v>2.237635850906372</v>
+        <v>2.078203201293945</v>
       </c>
       <c r="G25" t="n">
-        <v>2.301235675811768</v>
+        <v>2.238305807113647</v>
       </c>
       <c r="H25" t="n">
-        <v>2.14052939414978</v>
+        <v>2.250753164291382</v>
       </c>
       <c r="I25" t="n">
-        <v>2.250320672988892</v>
+        <v>2.09318995475769</v>
       </c>
       <c r="J25" t="n">
-        <v>2.020912647247314</v>
+        <v>2.282173633575439</v>
       </c>
       <c r="K25" t="n">
-        <v>2.079349517822266</v>
+        <v>2.290149688720703</v>
       </c>
       <c r="L25" t="n">
-        <v>2.18939368724823</v>
+        <v>2.212942790985108</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.596354961395264</v>
+        <v>2.346015691757202</v>
       </c>
       <c r="C26" t="n">
-        <v>2.486159324645996</v>
+        <v>2.614328861236572</v>
       </c>
       <c r="D26" t="n">
-        <v>2.415842056274414</v>
+        <v>2.44674825668335</v>
       </c>
       <c r="E26" t="n">
-        <v>2.548625707626343</v>
+        <v>2.296665191650391</v>
       </c>
       <c r="F26" t="n">
-        <v>2.199264049530029</v>
+        <v>2.399882793426514</v>
       </c>
       <c r="G26" t="n">
-        <v>2.318970918655396</v>
+        <v>2.862214326858521</v>
       </c>
       <c r="H26" t="n">
-        <v>2.310810327529907</v>
+        <v>2.479179859161377</v>
       </c>
       <c r="I26" t="n">
-        <v>2.571846961975098</v>
+        <v>2.396387815475464</v>
       </c>
       <c r="J26" t="n">
-        <v>2.248876333236694</v>
+        <v>2.743006467819214</v>
       </c>
       <c r="K26" t="n">
-        <v>2.61363673210144</v>
+        <v>2.555966377258301</v>
       </c>
       <c r="L26" t="n">
-        <v>2.431038737297058</v>
+        <v>2.51403956413269</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.135486364364624</v>
+        <v>2.180932760238647</v>
       </c>
       <c r="C27" t="n">
-        <v>2.107088327407837</v>
+        <v>2.098140716552734</v>
       </c>
       <c r="D27" t="n">
-        <v>2.046766519546509</v>
+        <v>2.238811492919922</v>
       </c>
       <c r="E27" t="n">
-        <v>2.087799072265625</v>
+        <v>2.236286163330078</v>
       </c>
       <c r="F27" t="n">
-        <v>2.282591581344604</v>
+        <v>2.121087551116943</v>
       </c>
       <c r="G27" t="n">
-        <v>2.324405431747437</v>
+        <v>2.187428712844849</v>
       </c>
       <c r="H27" t="n">
-        <v>2.141132831573486</v>
+        <v>2.3465576171875</v>
       </c>
       <c r="I27" t="n">
-        <v>2.288915634155273</v>
+        <v>2.363981962203979</v>
       </c>
       <c r="J27" t="n">
-        <v>2.118921756744385</v>
+        <v>2.300635576248169</v>
       </c>
       <c r="K27" t="n">
-        <v>2.231186389923096</v>
+        <v>2.188427686691284</v>
       </c>
       <c r="L27" t="n">
-        <v>2.176429390907288</v>
+        <v>2.226229023933411</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.124964952468872</v>
+        <v>2.043773412704468</v>
       </c>
       <c r="C28" t="n">
-        <v>2.020492315292358</v>
+        <v>2.214357137680054</v>
       </c>
       <c r="D28" t="n">
-        <v>2.137071132659912</v>
+        <v>2.204391479492188</v>
       </c>
       <c r="E28" t="n">
-        <v>2.164374828338623</v>
+        <v>2.256750822067261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.256676912307739</v>
+        <v>2.181431770324707</v>
       </c>
       <c r="G28" t="n">
-        <v>2.154815196990967</v>
+        <v>2.249258279800415</v>
       </c>
       <c r="H28" t="n">
-        <v>2.40771222114563</v>
+        <v>2.205370426177979</v>
       </c>
       <c r="I28" t="n">
-        <v>2.025478601455688</v>
+        <v>2.234294891357422</v>
       </c>
       <c r="J28" t="n">
-        <v>2.28519868850708</v>
+        <v>2.178457498550415</v>
       </c>
       <c r="K28" t="n">
-        <v>2.158819913864136</v>
+        <v>2.220324993133545</v>
       </c>
       <c r="L28" t="n">
-        <v>2.173560476303101</v>
+        <v>2.198841071128845</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.225414991378784</v>
+        <v>2.238804340362549</v>
       </c>
       <c r="C29" t="n">
-        <v>2.323515176773071</v>
+        <v>2.214362621307373</v>
       </c>
       <c r="D29" t="n">
-        <v>2.176603317260742</v>
+        <v>2.156005620956421</v>
       </c>
       <c r="E29" t="n">
-        <v>2.129876375198364</v>
+        <v>2.356018781661987</v>
       </c>
       <c r="F29" t="n">
-        <v>2.185277700424194</v>
+        <v>2.340534687042236</v>
       </c>
       <c r="G29" t="n">
-        <v>2.124325752258301</v>
+        <v>2.207378387451172</v>
       </c>
       <c r="H29" t="n">
-        <v>2.197034358978271</v>
+        <v>2.142534494400024</v>
       </c>
       <c r="I29" t="n">
-        <v>2.197574853897095</v>
+        <v>2.29863715171814</v>
       </c>
       <c r="J29" t="n">
-        <v>2.096529006958008</v>
+        <v>2.143022298812866</v>
       </c>
       <c r="K29" t="n">
-        <v>2.248286485671997</v>
+        <v>2.153995513916016</v>
       </c>
       <c r="L29" t="n">
-        <v>2.190443801879883</v>
+        <v>2.225129389762878</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.17442774772644</v>
+        <v>2.25722861289978</v>
       </c>
       <c r="C30" t="n">
-        <v>2.363722324371338</v>
+        <v>2.271703243255615</v>
       </c>
       <c r="D30" t="n">
-        <v>2.285767078399658</v>
+        <v>2.194402694702148</v>
       </c>
       <c r="E30" t="n">
-        <v>2.211645841598511</v>
+        <v>2.570944786071777</v>
       </c>
       <c r="F30" t="n">
-        <v>2.39506196975708</v>
+        <v>2.179448127746582</v>
       </c>
       <c r="G30" t="n">
-        <v>2.132197380065918</v>
+        <v>2.204374074935913</v>
       </c>
       <c r="H30" t="n">
-        <v>2.272920846939087</v>
+        <v>2.306628465652466</v>
       </c>
       <c r="I30" t="n">
-        <v>2.32410740852356</v>
+        <v>2.514084577560425</v>
       </c>
       <c r="J30" t="n">
-        <v>2.223406553268433</v>
+        <v>2.220330715179443</v>
       </c>
       <c r="K30" t="n">
-        <v>2.10033130645752</v>
+        <v>2.186429977416992</v>
       </c>
       <c r="L30" t="n">
-        <v>2.248358845710754</v>
+        <v>2.290557527542114</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.947844982147217</v>
+        <v>1.882696151733398</v>
       </c>
       <c r="C31" t="n">
-        <v>1.966464519500732</v>
+        <v>2.006908655166626</v>
       </c>
       <c r="D31" t="n">
-        <v>1.867562055587769</v>
+        <v>2.078202724456787</v>
       </c>
       <c r="E31" t="n">
-        <v>1.962267637252808</v>
+        <v>1.975966930389404</v>
       </c>
       <c r="F31" t="n">
-        <v>1.937817811965942</v>
+        <v>1.944527864456177</v>
       </c>
       <c r="G31" t="n">
-        <v>2.055156946182251</v>
+        <v>1.951038599014282</v>
       </c>
       <c r="H31" t="n">
-        <v>1.861518383026123</v>
+        <v>1.95452094078064</v>
       </c>
       <c r="I31" t="n">
-        <v>1.973164081573486</v>
+        <v>1.872719764709473</v>
       </c>
       <c r="J31" t="n">
-        <v>1.846753358840942</v>
+        <v>1.807383060455322</v>
       </c>
       <c r="K31" t="n">
-        <v>1.878646612167358</v>
+        <v>1.955522060394287</v>
       </c>
       <c r="L31" t="n">
-        <v>1.929719638824463</v>
+        <v>1.94294867515564</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.012868642807007</v>
+        <v>2.090189933776855</v>
       </c>
       <c r="C32" t="n">
-        <v>2.185619115829468</v>
+        <v>2.042778015136719</v>
       </c>
       <c r="D32" t="n">
-        <v>2.081214189529419</v>
+        <v>2.244777917861938</v>
       </c>
       <c r="E32" t="n">
-        <v>2.063835144042969</v>
+        <v>2.023834466934204</v>
       </c>
       <c r="F32" t="n">
-        <v>1.962426900863647</v>
+        <v>2.042794466018677</v>
       </c>
       <c r="G32" t="n">
-        <v>2.069632530212402</v>
+        <v>2.039301633834839</v>
       </c>
       <c r="H32" t="n">
-        <v>2.028673887252808</v>
+        <v>2.049772500991821</v>
       </c>
       <c r="I32" t="n">
-        <v>2.129363536834717</v>
+        <v>2.083223581314087</v>
       </c>
       <c r="J32" t="n">
-        <v>2.029033184051514</v>
+        <v>2.332543134689331</v>
       </c>
       <c r="K32" t="n">
-        <v>2.015851497650146</v>
+        <v>2.095155239105225</v>
       </c>
       <c r="L32" t="n">
-        <v>2.05785186290741</v>
+        <v>2.10443708896637</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.50796914100647</v>
+        <v>2.191412448883057</v>
       </c>
       <c r="C33" t="n">
-        <v>2.238332509994507</v>
+        <v>2.273719787597656</v>
       </c>
       <c r="D33" t="n">
-        <v>2.070304155349731</v>
+        <v>2.121094703674316</v>
       </c>
       <c r="E33" t="n">
-        <v>2.188709020614624</v>
+        <v>2.028813362121582</v>
       </c>
       <c r="F33" t="n">
-        <v>2.249169826507568</v>
+        <v>2.233302354812622</v>
       </c>
       <c r="G33" t="n">
-        <v>2.008272647857666</v>
+        <v>2.173453569412231</v>
       </c>
       <c r="H33" t="n">
-        <v>2.278469324111938</v>
+        <v>2.315592050552368</v>
       </c>
       <c r="I33" t="n">
-        <v>2.064720630645752</v>
+        <v>2.070215940475464</v>
       </c>
       <c r="J33" t="n">
-        <v>2.199228048324585</v>
+        <v>2.076208829879761</v>
       </c>
       <c r="K33" t="n">
-        <v>2.09139347076416</v>
+        <v>2.152002096176147</v>
       </c>
       <c r="L33" t="n">
-        <v>2.1896568775177</v>
+        <v>2.16358151435852</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>2.096697807312012</v>
+        <v>1.940545320510864</v>
       </c>
       <c r="C34" t="n">
-        <v>2.103161334991455</v>
+        <v>1.942062616348267</v>
       </c>
       <c r="D34" t="n">
-        <v>2.145041227340698</v>
+        <v>2.124082803726196</v>
       </c>
       <c r="E34" t="n">
-        <v>2.002863645553589</v>
+        <v>2.223204851150513</v>
       </c>
       <c r="F34" t="n">
-        <v>2.037990093231201</v>
+        <v>1.945047378540039</v>
       </c>
       <c r="G34" t="n">
-        <v>2.02798318862915</v>
+        <v>1.866228818893433</v>
       </c>
       <c r="H34" t="n">
-        <v>1.960616588592529</v>
+        <v>1.989931106567383</v>
       </c>
       <c r="I34" t="n">
-        <v>2.012994289398193</v>
+        <v>2.052269697189331</v>
       </c>
       <c r="J34" t="n">
-        <v>2.009339570999146</v>
+        <v>1.944538354873657</v>
       </c>
       <c r="K34" t="n">
-        <v>1.867291688919067</v>
+        <v>1.915612697601318</v>
       </c>
       <c r="L34" t="n">
-        <v>2.026397943496704</v>
+        <v>1.9943523645401</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.531514883041382</v>
+        <v>2.550498723983765</v>
       </c>
       <c r="C35" t="n">
-        <v>2.447122097015381</v>
+        <v>2.449792861938477</v>
       </c>
       <c r="D35" t="n">
-        <v>2.525051116943359</v>
+        <v>2.391906976699829</v>
       </c>
       <c r="E35" t="n">
-        <v>2.554224014282227</v>
+        <v>2.626302480697632</v>
       </c>
       <c r="F35" t="n">
-        <v>2.428701877593994</v>
+        <v>2.560472249984741</v>
       </c>
       <c r="G35" t="n">
-        <v>2.538913488388062</v>
+        <v>2.620305776596069</v>
       </c>
       <c r="H35" t="n">
-        <v>2.372541904449463</v>
+        <v>2.434787273406982</v>
       </c>
       <c r="I35" t="n">
-        <v>2.434355735778809</v>
+        <v>2.414846420288086</v>
       </c>
       <c r="J35" t="n">
-        <v>2.487555742263794</v>
+        <v>2.535555601119995</v>
       </c>
       <c r="K35" t="n">
-        <v>2.400343656539917</v>
+        <v>2.756483554840088</v>
       </c>
       <c r="L35" t="n">
-        <v>2.472032451629639</v>
+        <v>2.534095191955566</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1.909019470214844</v>
+        <v>2.061250925064087</v>
       </c>
       <c r="C36" t="n">
-        <v>2.061604738235474</v>
+        <v>2.141045570373535</v>
       </c>
       <c r="D36" t="n">
-        <v>1.85474681854248</v>
+        <v>2.123105049133301</v>
       </c>
       <c r="E36" t="n">
-        <v>1.972447872161865</v>
+        <v>2.259752750396729</v>
       </c>
       <c r="F36" t="n">
-        <v>2.023143529891968</v>
+        <v>2.14902138710022</v>
       </c>
       <c r="G36" t="n">
-        <v>1.933704137802124</v>
+        <v>2.023360967636108</v>
       </c>
       <c r="H36" t="n">
-        <v>1.956902980804443</v>
+        <v>2.137050628662109</v>
       </c>
       <c r="I36" t="n">
-        <v>2.103533506393433</v>
+        <v>2.141055345535278</v>
       </c>
       <c r="J36" t="n">
-        <v>1.919589042663574</v>
+        <v>3.48849892616272</v>
       </c>
       <c r="K36" t="n">
-        <v>2.148407936096191</v>
+        <v>1.988829135894775</v>
       </c>
       <c r="L36" t="n">
-        <v>1.98831000328064</v>
+        <v>2.251297068595886</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.4285728931427</v>
+        <v>2.342424154281616</v>
       </c>
       <c r="C37" t="n">
-        <v>2.277146100997925</v>
+        <v>2.317475318908691</v>
       </c>
       <c r="D37" t="n">
-        <v>2.234407901763916</v>
+        <v>2.347890615463257</v>
       </c>
       <c r="E37" t="n">
-        <v>2.220078706741333</v>
+        <v>2.307491302490234</v>
       </c>
       <c r="F37" t="n">
-        <v>2.261121273040771</v>
+        <v>2.203258514404297</v>
       </c>
       <c r="G37" t="n">
-        <v>2.340567827224731</v>
+        <v>2.248164653778076</v>
       </c>
       <c r="H37" t="n">
-        <v>2.164994716644287</v>
+        <v>2.442659139633179</v>
       </c>
       <c r="I37" t="n">
-        <v>2.38988184928894</v>
+        <v>2.607846021652222</v>
       </c>
       <c r="J37" t="n">
-        <v>2.363744974136353</v>
+        <v>2.50598669052124</v>
       </c>
       <c r="K37" t="n">
-        <v>2.145759105682373</v>
+        <v>2.503997087478638</v>
       </c>
       <c r="L37" t="n">
-        <v>2.282627534866333</v>
+        <v>2.382719349861145</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.640333890914917</v>
+        <v>2.615209102630615</v>
       </c>
       <c r="C38" t="n">
-        <v>2.501626491546631</v>
+        <v>2.55583667755127</v>
       </c>
       <c r="D38" t="n">
-        <v>2.561947822570801</v>
+        <v>2.651598930358887</v>
       </c>
       <c r="E38" t="n">
-        <v>2.609760522842407</v>
+        <v>3.096458673477173</v>
       </c>
       <c r="F38" t="n">
-        <v>2.721046447753906</v>
+        <v>2.579778432846069</v>
       </c>
       <c r="G38" t="n">
-        <v>2.588070154190063</v>
+        <v>2.63065505027771</v>
       </c>
       <c r="H38" t="n">
-        <v>2.709351778030396</v>
+        <v>2.572788238525391</v>
       </c>
       <c r="I38" t="n">
-        <v>2.506671667098999</v>
+        <v>2.676521778106689</v>
       </c>
       <c r="J38" t="n">
-        <v>2.613935947418213</v>
+        <v>2.511962652206421</v>
       </c>
       <c r="K38" t="n">
-        <v>2.545025825500488</v>
+        <v>2.591245412826538</v>
       </c>
       <c r="L38" t="n">
-        <v>2.599777054786682</v>
+        <v>2.648205494880676</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.497740268707275</v>
+        <v>2.332415342330933</v>
       </c>
       <c r="C39" t="n">
-        <v>2.116508007049561</v>
+        <v>2.189324140548706</v>
       </c>
       <c r="D39" t="n">
-        <v>2.37060546875</v>
+        <v>2.33542013168335</v>
       </c>
       <c r="E39" t="n">
-        <v>2.399293899536133</v>
+        <v>2.312465190887451</v>
       </c>
       <c r="F39" t="n">
-        <v>2.454317569732666</v>
+        <v>2.448124170303345</v>
       </c>
       <c r="G39" t="n">
-        <v>2.295294761657715</v>
+        <v>2.385775566101074</v>
       </c>
       <c r="H39" t="n">
-        <v>2.305379867553711</v>
+        <v>2.271078586578369</v>
       </c>
       <c r="I39" t="n">
-        <v>2.281108617782593</v>
+        <v>2.592248439788818</v>
       </c>
       <c r="J39" t="n">
-        <v>2.359583139419556</v>
+        <v>2.284552812576294</v>
       </c>
       <c r="K39" t="n">
-        <v>2.514131546020508</v>
+        <v>2.446639060974121</v>
       </c>
       <c r="L39" t="n">
-        <v>2.359396314620972</v>
+        <v>2.359804344177246</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.236731767654419</v>
+        <v>2.172840595245361</v>
       </c>
       <c r="C40" t="n">
-        <v>2.275276660919189</v>
+        <v>2.271584272384644</v>
       </c>
       <c r="D40" t="n">
-        <v>2.214780330657959</v>
+        <v>2.18631649017334</v>
       </c>
       <c r="E40" t="n">
-        <v>2.23594856262207</v>
+        <v>2.160893678665161</v>
       </c>
       <c r="F40" t="n">
-        <v>2.121972799301147</v>
+        <v>2.023231267929077</v>
       </c>
       <c r="G40" t="n">
-        <v>2.195948123931885</v>
+        <v>2.189786672592163</v>
       </c>
       <c r="H40" t="n">
-        <v>2.187427759170532</v>
+        <v>2.134451866149902</v>
       </c>
       <c r="I40" t="n">
-        <v>2.170424699783325</v>
+        <v>2.153877258300781</v>
       </c>
       <c r="J40" t="n">
-        <v>2.212435722351074</v>
+        <v>2.227708578109741</v>
       </c>
       <c r="K40" t="n">
-        <v>2.134018898010254</v>
+        <v>2.482551336288452</v>
       </c>
       <c r="L40" t="n">
-        <v>2.198496532440186</v>
+        <v>2.200324201583862</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.568335771560669</v>
+        <v>2.402469635009766</v>
       </c>
       <c r="C41" t="n">
-        <v>2.57344126701355</v>
+        <v>2.526448249816895</v>
       </c>
       <c r="D41" t="n">
-        <v>2.44353199005127</v>
+        <v>2.321459531784058</v>
       </c>
       <c r="E41" t="n">
-        <v>2.46318793296814</v>
+        <v>2.328447103500366</v>
       </c>
       <c r="F41" t="n">
-        <v>2.280547380447388</v>
+        <v>2.509976863861084</v>
       </c>
       <c r="G41" t="n">
-        <v>2.333549737930298</v>
+        <v>2.502006530761719</v>
       </c>
       <c r="H41" t="n">
-        <v>2.492435455322266</v>
+        <v>2.323443174362183</v>
       </c>
       <c r="I41" t="n">
-        <v>2.315099239349365</v>
+        <v>2.274579286575317</v>
       </c>
       <c r="J41" t="n">
-        <v>2.567107677459717</v>
+        <v>2.406732320785522</v>
       </c>
       <c r="K41" t="n">
-        <v>2.526119709014893</v>
+        <v>2.393768310546875</v>
       </c>
       <c r="L41" t="n">
-        <v>2.456335616111756</v>
+        <v>2.398933100700378</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>2.685224533081055</v>
+        <v>2.056640625</v>
       </c>
       <c r="C42" t="n">
-        <v>2.094099044799805</v>
+        <v>2.054150342941284</v>
       </c>
       <c r="D42" t="n">
-        <v>2.151522636413574</v>
+        <v>2.059633493423462</v>
       </c>
       <c r="E42" t="n">
-        <v>2.158568143844604</v>
+        <v>2.219725370407104</v>
       </c>
       <c r="F42" t="n">
-        <v>2.156429529190063</v>
+        <v>2.183813333511353</v>
       </c>
       <c r="G42" t="n">
-        <v>2.262997388839722</v>
+        <v>2.070112943649292</v>
       </c>
       <c r="H42" t="n">
-        <v>2.252012968063354</v>
+        <v>2.137927055358887</v>
       </c>
       <c r="I42" t="n">
-        <v>2.254768133163452</v>
+        <v>2.043182134628296</v>
       </c>
       <c r="J42" t="n">
-        <v>2.237545490264893</v>
+        <v>2.077584981918335</v>
       </c>
       <c r="K42" t="n">
-        <v>2.532803297042847</v>
+        <v>2.073107957839966</v>
       </c>
       <c r="L42" t="n">
-        <v>2.278597116470337</v>
+        <v>2.097587823867798</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.974121332168579</v>
+        <v>2.181325435638428</v>
       </c>
       <c r="C43" t="n">
-        <v>2.70264744758606</v>
+        <v>2.393779039382935</v>
       </c>
       <c r="D43" t="n">
-        <v>2.384968757629395</v>
+        <v>2.219216108322144</v>
       </c>
       <c r="E43" t="n">
-        <v>2.171234607696533</v>
+        <v>2.193277835845947</v>
       </c>
       <c r="F43" t="n">
-        <v>2.343643426895142</v>
+        <v>2.207245111465454</v>
       </c>
       <c r="G43" t="n">
-        <v>2.393125772476196</v>
+        <v>2.299519062042236</v>
       </c>
       <c r="H43" t="n">
-        <v>2.741243124008179</v>
+        <v>2.190290689468384</v>
       </c>
       <c r="I43" t="n">
-        <v>2.221777677536011</v>
+        <v>2.166850328445435</v>
       </c>
       <c r="J43" t="n">
-        <v>2.307588338851929</v>
+        <v>2.086065769195557</v>
       </c>
       <c r="K43" t="n">
-        <v>2.152155637741089</v>
+        <v>2.086110591888428</v>
       </c>
       <c r="L43" t="n">
-        <v>2.439250612258911</v>
+        <v>2.202367997169495</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.175838708877563</v>
+        <v>2.148404836654663</v>
       </c>
       <c r="C44" t="n">
-        <v>2.144127368927002</v>
+        <v>2.237168550491333</v>
       </c>
       <c r="D44" t="n">
-        <v>2.119876623153687</v>
+        <v>2.208245038986206</v>
       </c>
       <c r="E44" t="n">
-        <v>2.079212427139282</v>
+        <v>2.171351432800293</v>
       </c>
       <c r="F44" t="n">
-        <v>2.037885665893555</v>
+        <v>2.111990451812744</v>
       </c>
       <c r="G44" t="n">
-        <v>2.363631010055542</v>
+        <v>2.201280355453491</v>
       </c>
       <c r="H44" t="n">
-        <v>2.310759305953979</v>
+        <v>2.257596492767334</v>
       </c>
       <c r="I44" t="n">
-        <v>2.239405393600464</v>
+        <v>2.160513877868652</v>
       </c>
       <c r="J44" t="n">
-        <v>2.119489669799805</v>
+        <v>2.191411256790161</v>
       </c>
       <c r="K44" t="n">
-        <v>2.114403009414673</v>
+        <v>2.207389116287231</v>
       </c>
       <c r="L44" t="n">
-        <v>2.170462918281555</v>
+        <v>2.189535140991211</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>2.109044075012207</v>
+        <v>2.041804313659668</v>
       </c>
       <c r="C45" t="n">
-        <v>2.108493089675903</v>
+        <v>2.061236381530762</v>
       </c>
       <c r="D45" t="n">
-        <v>2.019901752471924</v>
+        <v>1.969988822937012</v>
       </c>
       <c r="E45" t="n">
-        <v>2.087934255599976</v>
+        <v>1.913611888885498</v>
       </c>
       <c r="F45" t="n">
-        <v>1.957523584365845</v>
+        <v>1.974462270736694</v>
       </c>
       <c r="G45" t="n">
-        <v>2.348260641098022</v>
+        <v>1.945045232772827</v>
       </c>
       <c r="H45" t="n">
-        <v>1.931127309799194</v>
+        <v>2.086177349090576</v>
       </c>
       <c r="I45" t="n">
-        <v>2.035191297531128</v>
+        <v>1.994930267333984</v>
       </c>
       <c r="J45" t="n">
-        <v>2.036993503570557</v>
+        <v>1.909646272659302</v>
       </c>
       <c r="K45" t="n">
-        <v>2.075462579727173</v>
+        <v>1.903647899627686</v>
       </c>
       <c r="L45" t="n">
-        <v>2.070993208885193</v>
+        <v>1.980055069923401</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1.892242908477783</v>
+        <v>1.911625862121582</v>
       </c>
       <c r="C46" t="n">
-        <v>1.849943161010742</v>
+        <v>1.876711368560791</v>
       </c>
       <c r="D46" t="n">
-        <v>1.929130077362061</v>
+        <v>1.859248399734497</v>
       </c>
       <c r="E46" t="n">
-        <v>2.060709953308105</v>
+        <v>1.843802928924561</v>
       </c>
       <c r="F46" t="n">
-        <v>1.889383316040039</v>
+        <v>2.211377859115601</v>
       </c>
       <c r="G46" t="n">
-        <v>2.078059196472168</v>
+        <v>2.132058620452881</v>
       </c>
       <c r="H46" t="n">
-        <v>1.837625980377197</v>
+        <v>1.925583124160767</v>
       </c>
       <c r="I46" t="n">
-        <v>1.861167669296265</v>
+        <v>1.916608333587646</v>
       </c>
       <c r="J46" t="n">
-        <v>1.941871166229248</v>
+        <v>2.093153953552246</v>
       </c>
       <c r="K46" t="n">
-        <v>2.000047206878662</v>
+        <v>2.03180980682373</v>
       </c>
       <c r="L46" t="n">
-        <v>1.934018063545227</v>
+        <v>1.98019802570343</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.718582630157471</v>
+        <v>2.636273384094238</v>
       </c>
       <c r="C47" t="n">
-        <v>2.582668542861938</v>
+        <v>2.779907703399658</v>
       </c>
       <c r="D47" t="n">
-        <v>2.835448980331421</v>
+        <v>2.672175168991089</v>
       </c>
       <c r="E47" t="n">
-        <v>2.793908596038818</v>
+        <v>2.92506742477417</v>
       </c>
       <c r="F47" t="n">
-        <v>2.750342845916748</v>
+        <v>3.047742605209351</v>
       </c>
       <c r="G47" t="n">
-        <v>2.608942270278931</v>
+        <v>2.742532968521118</v>
       </c>
       <c r="H47" t="n">
-        <v>2.74334716796875</v>
+        <v>2.960446357727051</v>
       </c>
       <c r="I47" t="n">
-        <v>2.464937210083008</v>
+        <v>2.712586164474487</v>
       </c>
       <c r="J47" t="n">
-        <v>2.789504051208496</v>
+        <v>2.834760665893555</v>
       </c>
       <c r="K47" t="n">
-        <v>2.896147727966309</v>
+        <v>2.716559171676636</v>
       </c>
       <c r="L47" t="n">
-        <v>2.718383002281189</v>
+        <v>2.802805161476135</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.306183338165283</v>
+        <v>2.435298919677734</v>
       </c>
       <c r="C48" t="n">
-        <v>2.294556617736816</v>
+        <v>2.309609413146973</v>
       </c>
       <c r="D48" t="n">
-        <v>2.29233980178833</v>
+        <v>2.271190881729126</v>
       </c>
       <c r="E48" t="n">
-        <v>2.305622577667236</v>
+        <v>2.274701833724976</v>
       </c>
       <c r="F48" t="n">
-        <v>2.265888452529907</v>
+        <v>2.309610605239868</v>
       </c>
       <c r="G48" t="n">
-        <v>2.241044044494629</v>
+        <v>2.235301733016968</v>
       </c>
       <c r="H48" t="n">
-        <v>2.295903205871582</v>
+        <v>2.231816530227661</v>
       </c>
       <c r="I48" t="n">
-        <v>2.338271617889404</v>
+        <v>2.281184673309326</v>
       </c>
       <c r="J48" t="n">
-        <v>2.230884552001953</v>
+        <v>2.515611171722412</v>
       </c>
       <c r="K48" t="n">
-        <v>2.248564958572388</v>
+        <v>2.42482328414917</v>
       </c>
       <c r="L48" t="n">
-        <v>2.281925916671753</v>
+        <v>2.328914904594421</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.378960609436035</v>
+        <v>2.390905857086182</v>
       </c>
       <c r="C49" t="n">
-        <v>2.446558475494385</v>
+        <v>2.338524580001831</v>
       </c>
       <c r="D49" t="n">
-        <v>2.360115766525269</v>
+        <v>2.50811243057251</v>
       </c>
       <c r="E49" t="n">
-        <v>2.370204210281372</v>
+        <v>2.439767837524414</v>
       </c>
       <c r="F49" t="n">
-        <v>2.338284254074097</v>
+        <v>2.365972280502319</v>
       </c>
       <c r="G49" t="n">
-        <v>2.393853902816772</v>
+        <v>2.438774108886719</v>
       </c>
       <c r="H49" t="n">
-        <v>2.291598796844482</v>
+        <v>2.309616088867188</v>
       </c>
       <c r="I49" t="n">
-        <v>2.459822654724121</v>
+        <v>2.358989477157593</v>
       </c>
       <c r="J49" t="n">
-        <v>2.618853569030762</v>
+        <v>2.373943328857422</v>
       </c>
       <c r="K49" t="n">
-        <v>2.346783876419067</v>
+        <v>2.388404607772827</v>
       </c>
       <c r="L49" t="n">
-        <v>2.400503611564636</v>
+        <v>2.3913010597229</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.074604511260986</v>
+        <v>2.060733556747437</v>
       </c>
       <c r="C50" t="n">
-        <v>2.108721256256104</v>
+        <v>2.039318799972534</v>
       </c>
       <c r="D50" t="n">
-        <v>2.096580505371094</v>
+        <v>2.078692674636841</v>
       </c>
       <c r="E50" t="n">
-        <v>2.062482595443726</v>
+        <v>2.212387800216675</v>
       </c>
       <c r="F50" t="n">
-        <v>2.35475492477417</v>
+        <v>2.042300462722778</v>
       </c>
       <c r="G50" t="n">
-        <v>2.060100078582764</v>
+        <v>2.080207586288452</v>
       </c>
       <c r="H50" t="n">
-        <v>2.118450164794922</v>
+        <v>2.096158504486084</v>
       </c>
       <c r="I50" t="n">
-        <v>2.236076593399048</v>
+        <v>2.103145360946655</v>
       </c>
       <c r="J50" t="n">
-        <v>2.101945400238037</v>
+        <v>2.153013467788696</v>
       </c>
       <c r="K50" t="n">
-        <v>1.978301525115967</v>
+        <v>2.229312181472778</v>
       </c>
       <c r="L50" t="n">
-        <v>2.119201755523682</v>
+        <v>2.109527039527893</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1.910462379455566</v>
+        <v>2.047278165817261</v>
       </c>
       <c r="C51" t="n">
-        <v>1.981719732284546</v>
+        <v>2.158987760543823</v>
       </c>
       <c r="D51" t="n">
-        <v>1.996514558792114</v>
+        <v>2.060261249542236</v>
       </c>
       <c r="E51" t="n">
-        <v>2.030158996582031</v>
+        <v>2.038805723190308</v>
       </c>
       <c r="F51" t="n">
-        <v>1.914359092712402</v>
+        <v>1.998906135559082</v>
       </c>
       <c r="G51" t="n">
-        <v>2.064018964767456</v>
+        <v>2.380955934524536</v>
       </c>
       <c r="H51" t="n">
-        <v>1.978597640991211</v>
+        <v>2.017853498458862</v>
       </c>
       <c r="I51" t="n">
-        <v>2.048095464706421</v>
+        <v>2.077222347259521</v>
       </c>
       <c r="J51" t="n">
-        <v>1.918667554855347</v>
+        <v>2.085345506668091</v>
       </c>
       <c r="K51" t="n">
-        <v>1.938238382339478</v>
+        <v>2.052651405334473</v>
       </c>
       <c r="L51" t="n">
-        <v>1.978083276748657</v>
+        <v>2.091826772689819</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.30274199962616</v>
+        <v>2.272009482383728</v>
       </c>
       <c r="C52" t="n">
-        <v>2.254519634246826</v>
+        <v>2.293455185890198</v>
       </c>
       <c r="D52" t="n">
-        <v>2.222345614433288</v>
+        <v>2.292884192466736</v>
       </c>
       <c r="E52" t="n">
-        <v>2.234837965965271</v>
+        <v>2.319522042274475</v>
       </c>
       <c r="F52" t="n">
-        <v>2.251319417953491</v>
+        <v>2.275656862258911</v>
       </c>
       <c r="G52" t="n">
-        <v>2.260990085601807</v>
+        <v>2.282675647735596</v>
       </c>
       <c r="H52" t="n">
-        <v>2.253164086341858</v>
+        <v>2.298622679710388</v>
       </c>
       <c r="I52" t="n">
-        <v>2.270504727363587</v>
+        <v>2.29841558933258</v>
       </c>
       <c r="J52" t="n">
-        <v>2.279480953216553</v>
+        <v>2.325164632797241</v>
       </c>
       <c r="K52" t="n">
-        <v>2.259603219032288</v>
+        <v>2.332466583251953</v>
       </c>
       <c r="L52" t="n">
-        <v>2.258950770378113</v>
+        <v>2.29908728981018</v>
       </c>
     </row>
   </sheetData>
